--- a/output/pdf_financials_xlsx/KVM.xlsx
+++ b/output/pdf_financials_xlsx/KVM.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.154099</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.154099</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.154099</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-3.934836</v>
+        <v>3.934836</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>1.926238</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.154099</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.154099</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.550877</v>
+        <v>-0.550877</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.154099</v>
+        <v>-0.154099</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KVM.xlsx
+++ b/output/pdf_financials_xlsx/KVM.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.212133</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.048173</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017735</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.212133</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.048173</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017735</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.212671</v>
+        <v>0.000538</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.048688</v>
+        <v>0.000515</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.000515</v>
       </c>
     </row>
     <row r="49">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
